--- a/public/downloads/MeffordInterpreting2019.xlsx
+++ b/public/downloads/MeffordInterpreting2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -659,10 +682,10 @@
         <v>28</v>
       </c>
       <c r="N3" s="5">
-        <v>419.7243912220001</v>
+        <v>419724.3912220001</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03330617292667831</v>
+        <v>33.30617292667831</v>
       </c>
       <c r="P3" s="5">
         <v>12602</v>
@@ -709,10 +732,10 @@
         <v>28</v>
       </c>
       <c r="N4" s="5">
-        <v>651.8990499973297</v>
+        <v>651899.0499973297</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08293881043223024</v>
+        <v>82.93881043223024</v>
       </c>
       <c r="P4" s="5">
         <v>7860</v>
@@ -759,10 +782,10 @@
         <v>28</v>
       </c>
       <c r="N5" s="5">
-        <v>1270.373911619186</v>
+        <v>1270373.911619186</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1519767809091023</v>
+        <v>151.9767809091023</v>
       </c>
       <c r="P5" s="5">
         <v>8359</v>
@@ -809,10 +832,10 @@
         <v>28</v>
       </c>
       <c r="N6" s="5">
-        <v>768.756471157074</v>
+        <v>768756.471157074</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09198952628420175</v>
+        <v>91.98952628420174</v>
       </c>
       <c r="P6" s="5">
         <v>8357</v>
@@ -859,10 +882,10 @@
         <v>28</v>
       </c>
       <c r="N7" s="5">
-        <v>1975.750643730164</v>
+        <v>1975750.643730164</v>
       </c>
       <c r="O7" s="4">
-        <v>0.368335317623073</v>
+        <v>368.335317623073</v>
       </c>
       <c r="P7" s="5">
         <v>5364</v>
@@ -909,10 +932,10 @@
         <v>28</v>
       </c>
       <c r="N8" s="5">
-        <v>264.7031228542328</v>
+        <v>264703.1228542328</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02549389606609196</v>
+        <v>25.49389606609196</v>
       </c>
       <c r="P8" s="5">
         <v>10383</v>
@@ -959,10 +982,10 @@
         <v>28</v>
       </c>
       <c r="N9" s="5">
-        <v>361.4096887111664</v>
+        <v>361409.6887111664</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03334345315168986</v>
+        <v>33.34345315168986</v>
       </c>
       <c r="P9" s="5">
         <v>10839</v>
@@ -1009,10 +1032,10 @@
         <v>28</v>
       </c>
       <c r="N10" s="5">
-        <v>602.3299250602722</v>
+        <v>602329.9250602722</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08859095823801622</v>
+        <v>88.59095823801621</v>
       </c>
       <c r="P10" s="5">
         <v>6799</v>
@@ -1059,10 +1082,10 @@
         <v>28</v>
       </c>
       <c r="N11" s="5">
-        <v>410.2483334541321</v>
+        <v>410248.3334541321</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04896733509836859</v>
+        <v>48.96733509836859</v>
       </c>
       <c r="P11" s="5">
         <v>8378</v>
@@ -1109,10 +1132,10 @@
         <v>28</v>
       </c>
       <c r="N12" s="5">
-        <v>250.2213883399963</v>
+        <v>250221.3883399963</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02683914923736955</v>
+        <v>26.83914923736955</v>
       </c>
       <c r="P12" s="5">
         <v>9323</v>
@@ -1159,10 +1182,10 @@
         <v>28</v>
       </c>
       <c r="N13" s="5">
-        <v>733.3975925445557</v>
+        <v>733397.5925445557</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07382701757042034</v>
+        <v>73.82701757042034</v>
       </c>
       <c r="P13" s="5">
         <v>9934</v>
@@ -1209,10 +1232,10 @@
         <v>28</v>
       </c>
       <c r="N14" s="5">
-        <v>5599.685429334641</v>
+        <v>5599685.429334641</v>
       </c>
       <c r="O14" s="4">
-        <v>0.5917452635881476</v>
+        <v>591.7452635881476</v>
       </c>
       <c r="P14" s="5">
         <v>9463</v>
@@ -1259,10 +1282,10 @@
         <v>28</v>
       </c>
       <c r="N15" s="5">
-        <v>3632.963635206223</v>
+        <v>3632963.635206223</v>
       </c>
       <c r="O15" s="4">
-        <v>0.5294321823384177</v>
+        <v>529.4321823384178</v>
       </c>
       <c r="P15" s="5">
         <v>6862</v>
@@ -1309,10 +1332,10 @@
         <v>28</v>
       </c>
       <c r="N16" s="5">
-        <v>1128.071286439896</v>
+        <v>1128071.286439896</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1104112054849658</v>
+        <v>110.4112054849658</v>
       </c>
       <c r="P16" s="5">
         <v>10217</v>
@@ -1359,10 +1382,10 @@
         <v>28</v>
       </c>
       <c r="N17" s="5">
-        <v>739.6232533454895</v>
+        <v>739623.2533454895</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1106723407669444</v>
+        <v>110.6723407669444</v>
       </c>
       <c r="P17" s="5">
         <v>6683</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,194 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2426048640946878</v>
+        <v>0.3564645006817482</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1667755480097162</v>
+        <v>0.3608445920374083</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1882699109601088</v>
+        <v>0.1796284445782435</v>
       </c>
       <c r="E3" s="4">
-        <v>84.92857142857143</v>
+        <v>71.92857142857143</v>
       </c>
       <c r="F3" s="4">
-        <v>80.18456375838926</v>
+        <v>58.16778523489933</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3564645006817482</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3608445920374083</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5634633398094571</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.09193737438022254</v>
-      </c>
+        <v>0.8896515554661575</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.288716381465863</v>
+        <v>0.3337874662224686</v>
       </c>
       <c r="E4" s="4">
-        <v>74.58427815570688</v>
+        <v>51.5759637188211</v>
       </c>
       <c r="F4" s="4">
-        <v>56.60949540144125</v>
+        <v>24.88068605518244</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8896515554661575</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2426510198769313</v>
+        <v>0.3844761345478019</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2006048188413828</v>
+        <v>0.2928817930063777</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1712140115841091</v>
+        <v>0.2178970066110859</v>
       </c>
       <c r="E5" s="4">
-        <v>82.13151927437661</v>
+        <v>65.759637188209</v>
       </c>
       <c r="F5" s="4">
-        <v>72.9791200596563</v>
+        <v>48.14690529455545</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>6</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.3844761345478019</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2928817930063777</v>
+      </c>
+      <c r="R5" s="5">
         <v>3</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1695,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1714,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1756,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1787,190 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2993455011015385</v>
+        <v>0.4679074398178614</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2373213160390378</v>
+        <v>0.3898915024676342</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1769406179797215</v>
+        <v>0.4381049995164631</v>
       </c>
       <c r="E3" s="4">
-        <v>81.79251700680273</v>
+        <v>66.49319727891159</v>
       </c>
       <c r="F3" s="4">
-        <v>69.94295302013423</v>
+        <v>52.73601789709147</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4679074398178614</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3898915024676342</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.091112926785204</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5458971824438095</v>
-      </c>
+        <v>0.6896359744594255</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.219228176516525</v>
+        <v>0.667213346639067</v>
       </c>
       <c r="E4" s="4">
-        <v>69.24036281179161</v>
+        <v>57.73998488284225</v>
       </c>
       <c r="F4" s="4">
-        <v>39.53268704946532</v>
+        <v>37.4011931394485</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6896359744594255</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5034240061715864</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2792633414021566</v>
-      </c>
+        <v>0.4520002807960282</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.2938465317689254</v>
+        <v>0.5261949906243015</v>
       </c>
       <c r="E5" s="4">
-        <v>78.52607709750572</v>
+        <v>63.95691609977339</v>
       </c>
       <c r="F5" s="4">
-        <v>62.07556549838445</v>
+        <v>42.36390753169331</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4520002807960282</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1981,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2000,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2042,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2073,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3452726774843768</v>
+        <v>0.2426048640946878</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1677344751709029</v>
+        <v>0.1667755480097162</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1777249998325146</v>
+        <v>0.1882699109601088</v>
       </c>
       <c r="E3" s="4">
-        <v>78.66326530612247</v>
+        <v>84.92857142857143</v>
       </c>
       <c r="F3" s="4">
-        <v>62.92170022371356</v>
+        <v>80.18456375838926</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1667755480097162</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1577326690443102</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09631362860316139</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.038522946088057</v>
+        <v>0.5634633398094571</v>
       </c>
       <c r="C4" s="4">
-        <v>0.08346303730229465</v>
+        <v>0.09193737438022254</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2451404125908678</v>
+        <v>0.288716381465863</v>
       </c>
       <c r="E4" s="4">
-        <v>67.53968253968281</v>
+        <v>74.58427815570688</v>
       </c>
       <c r="F4" s="4">
-        <v>36.69649515287059</v>
+        <v>56.60949540144125</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5634633398094571</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09193737438022254</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4562234698152628</v>
+        <v>0.2426510198769313</v>
       </c>
       <c r="C5" s="4">
-        <v>0.06515634374264323</v>
+        <v>0.2006048188413828</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1332861538188834</v>
+        <v>0.1712140115841091</v>
       </c>
       <c r="E5" s="4">
-        <v>72.11262282690893</v>
+        <v>82.13151927437661</v>
       </c>
       <c r="F5" s="4">
-        <v>46.26895351727552</v>
+        <v>72.9791200596563</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.108547192029835</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2371888087044905</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1772433323515642</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2279,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2287,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2298,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2340,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,107 +2371,159 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.263657218921378</v>
+        <v>0.2993455011015385</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3498683020105062</v>
+        <v>0.2373213160390378</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1700974492867431</v>
+        <v>0.1769406179797215</v>
       </c>
       <c r="E3" s="4">
-        <v>69.21428571428571</v>
+        <v>81.79251700680273</v>
       </c>
       <c r="F3" s="4">
-        <v>54.33892617449627</v>
+        <v>69.94295302013423</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2373213160390378</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3263166011234284</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2545256931624998</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9888079383479749</v>
+        <v>1.091112926785204</v>
       </c>
       <c r="C4" s="4">
-        <v>0.33725206879393</v>
+        <v>0.5458971824438095</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2540365218483518</v>
+        <v>0.219228176516525</v>
       </c>
       <c r="E4" s="4">
-        <v>57.04081632653092</v>
+        <v>69.24036281179161</v>
       </c>
       <c r="F4" s="4">
-        <v>41.52746706437927</v>
+        <v>39.53268704946532</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.091112926785204</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5458971824438095</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3562753096389442</v>
+        <v>0.5034240061715864</v>
       </c>
       <c r="C5" s="4">
-        <v>0.320986869541817</v>
+        <v>0.2792633414021566</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2485942439885775</v>
+        <v>0.2938465317689254</v>
       </c>
       <c r="E5" s="4">
-        <v>69.21390778533639</v>
+        <v>78.52607709750572</v>
       </c>
       <c r="F5" s="4">
-        <v>54.29903057419808</v>
+        <v>62.07556549838445</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -2222,9 +2546,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5034240061715864</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2792633414021566</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2575,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2594,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2636,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,40 +2667,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2920482300970317</v>
+        <v>0.3452726774843768</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1907358673868912</v>
+        <v>0.1677344751709029</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3027792141025204</v>
+        <v>0.1777249998325146</v>
       </c>
       <c r="E3" s="4">
-        <v>67.79251700680273</v>
+        <v>78.66326530612247</v>
       </c>
       <c r="F3" s="4">
-        <v>68.66666666666666</v>
+        <v>62.92170022371356</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>5</v>
@@ -2353,25 +2726,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3452726774843768</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1677344751709029</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3334205173595226</v>
+        <v>1.038522946088057</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05247671645914131</v>
+        <v>0.08346303730229465</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4805329834608837</v>
+        <v>0.2451404125908678</v>
       </c>
       <c r="E4" s="4">
-        <v>60.68405139833721</v>
+        <v>67.53968253968281</v>
       </c>
       <c r="F4" s="4">
-        <v>50.12552821277698</v>
+        <v>36.69649515287059</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2380,39 +2769,55 @@
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.038522946088057</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08346303730229465</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3879300641934106</v>
+        <v>0.4562234698152628</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1027030595558074</v>
+        <v>0.06515634374264323</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5371292922020623</v>
+        <v>0.1332861538188834</v>
       </c>
       <c r="E5" s="4">
-        <v>60.44595616024219</v>
+        <v>72.11262282690893</v>
       </c>
       <c r="F5" s="4">
-        <v>57.06189410887454</v>
+        <v>46.26895351727552</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -2435,9 +2840,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4562234698152628</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06515634374264323</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2869,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2888,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2930,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2961,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5075493999170423</v>
+        <v>0.263657218921378</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4229270822534072</v>
+        <v>0.3498683020105062</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3973736199388956</v>
+        <v>0.1700974492867431</v>
       </c>
       <c r="E3" s="4">
-        <v>83.54081632653062</v>
+        <v>69.21428571428571</v>
       </c>
       <c r="F3" s="4">
-        <v>73.80984340044743</v>
+        <v>54.33892617449627</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>6</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="P3" s="4">
+        <v>0.263657218921378</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3498683020105062</v>
+      </c>
+      <c r="R3" s="5">
         <v>4</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.249573433315158</v>
+        <v>0.9888079383479749</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5355158945242948</v>
+        <v>0.33725206879393</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5715444358731629</v>
+        <v>0.2540365218483518</v>
       </c>
       <c r="E4" s="4">
-        <v>76.53061224489819</v>
+        <v>57.04081632653092</v>
       </c>
       <c r="F4" s="4">
-        <v>61.5100671140946</v>
+        <v>41.52746706437927</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9888079383479749</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.33725206879393</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4890982001902384</v>
+        <v>0.3562753096389442</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2625634749697071</v>
+        <v>0.320986869541817</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2381814657471513</v>
+        <v>0.2485942439885775</v>
       </c>
       <c r="E5" s="4">
-        <v>79.87150415721857</v>
+        <v>69.21390778533639</v>
       </c>
       <c r="F5" s="4">
-        <v>69.60725826497726</v>
+        <v>54.29903057419808</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3562753096389442</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.320986869541817</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3163,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3171,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3182,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3224,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3255,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.539857962011058</v>
+        <v>0.2920482300970317</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5683447492140831</v>
+        <v>0.1907358673868912</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4482301980848863</v>
+        <v>0.3027792141025204</v>
       </c>
       <c r="E3" s="4">
-        <v>65.69387755102041</v>
+        <v>67.79251700680273</v>
       </c>
       <c r="F3" s="4">
-        <v>66.8847874720358</v>
+        <v>68.66666666666666</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -2779,25 +3314,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1418530639734317</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2525430630511768</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1968373716792405</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8484583528432454</v>
+        <v>0.3334205173595226</v>
       </c>
       <c r="C4" s="4">
-        <v>0.277461340292982</v>
+        <v>0.05247671645914131</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4810188030030134</v>
+        <v>0.4805329834608837</v>
       </c>
       <c r="E4" s="4">
-        <v>59.64852607709761</v>
+        <v>60.68405139833721</v>
       </c>
       <c r="F4" s="4">
-        <v>52.61744966442919</v>
+        <v>50.12552821277698</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2806,39 +3359,55 @@
         <v>1</v>
       </c>
       <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.3334205173595226</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05247671645914131</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2963395510685417</v>
+        <v>0.3879300641934106</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08549055969558594</v>
+        <v>0.1027030595558074</v>
       </c>
       <c r="D5" s="4">
-        <v>0.491173571326963</v>
+        <v>0.5371292922020623</v>
       </c>
       <c r="E5" s="4">
-        <v>60.21541950113392</v>
+        <v>60.44595616024219</v>
       </c>
       <c r="F5" s="4">
-        <v>54.66442953020123</v>
+        <v>57.06189410887454</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -2861,9 +3430,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3879300641934106</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1027030595558074</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3459,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3467,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3478,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3520,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3551,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4659586795020065</v>
+        <v>0.5075493999170423</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3389828919282009</v>
+        <v>0.4229270822534072</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3234769495974437</v>
+        <v>0.3973736199388956</v>
       </c>
       <c r="E3" s="4">
-        <v>86.41156462585032</v>
+        <v>83.54081632653062</v>
       </c>
       <c r="F3" s="4">
-        <v>77.18232662192436</v>
+        <v>73.80984340044743</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -2978,39 +3596,57 @@
         <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2632770284753286</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3870758785241752</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2474090632698549</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.097554045169054</v>
+        <v>1.249573433315158</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4207527488953933</v>
+        <v>0.5355158945242948</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4162056457497066</v>
+        <v>0.5715444358731629</v>
       </c>
       <c r="E4" s="4">
-        <v>79.05895691609979</v>
+        <v>76.53061224489819</v>
       </c>
       <c r="F4" s="4">
-        <v>61.72756649266623</v>
+        <v>61.5100671140946</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -3025,58 +3661,92 @@
         <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.249573433315158</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5355158945242948</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4682864371154618</v>
+        <v>0.4890982001902384</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2203383083890635</v>
+        <v>0.2625634749697071</v>
       </c>
       <c r="D5" s="4">
-        <v>0.229334105042756</v>
+        <v>0.2381814657471513</v>
       </c>
       <c r="E5" s="4">
-        <v>83.94179894179899</v>
+        <v>79.87150415721857</v>
       </c>
       <c r="F5" s="4">
-        <v>72.19736515038602</v>
+        <v>69.60725826497726</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1970388822756064</v>
+      </c>
+      <c r="O5" s="5">
         <v>5</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.3935780404470614</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1654530840932978</v>
+      </c>
+      <c r="R5" s="5">
         <v>5</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3757,1462 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.539857962011058</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5683447492140831</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4482301980848863</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.69387755102041</v>
+      </c>
+      <c r="F3" s="4">
+        <v>66.8847874720358</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1862088149317177</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3945830925578545</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4566194602550523</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.8484583528432454</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.277461340292982</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4810188030030134</v>
+      </c>
+      <c r="E4" s="4">
+        <v>59.64852607709761</v>
+      </c>
+      <c r="F4" s="4">
+        <v>52.61744966442919</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>5</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8484583528432454</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.277461340292982</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2963395510685417</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.08549055969558594</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.491173571326963</v>
+      </c>
+      <c r="E5" s="4">
+        <v>60.21541950113392</v>
+      </c>
+      <c r="F5" s="4">
+        <v>54.66442953020123</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2963395510685417</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08549055969558594</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4659586795020065</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3389828919282009</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3234769495974437</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.41156462585032</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.18232662192436</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1115000999891489</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3990586195085172</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.264649491935435</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.097554045169054</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4207527488953933</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4162056457497066</v>
+      </c>
+      <c r="E4" s="4">
+        <v>79.05895691609979</v>
+      </c>
+      <c r="F4" s="4">
+        <v>61.72756649266623</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.097554045169054</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4207527488953933</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4682864371154618</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2203383083890635</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.229334105042756</v>
+      </c>
+      <c r="E5" s="4">
+        <v>83.94179894179899</v>
+      </c>
+      <c r="F5" s="4">
+        <v>72.19736515038602</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4682864371154618</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2203383083890635</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D3" s="3">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F3" s="3">
+        <v>75</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6242203558258816</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.146397810495705</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.326971027602117</v>
+      </c>
+      <c r="K3" s="4">
+        <v>59.65743440233239</v>
+      </c>
+      <c r="L3" s="4">
+        <v>40.70469798657702</v>
+      </c>
+      <c r="M3" s="5">
+        <v>28</v>
+      </c>
+      <c r="N3" s="5">
+        <v>419724.3912220001</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.30617292667831</v>
+      </c>
+      <c r="P3" s="5">
+        <v>12602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.73637251960199</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4295994536906636</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.7475175383073979</v>
+      </c>
+      <c r="K4" s="4">
+        <v>77.74781341107871</v>
+      </c>
+      <c r="L4" s="4">
+        <v>58.42601470118228</v>
+      </c>
+      <c r="M4" s="5">
+        <v>28</v>
+      </c>
+      <c r="N4" s="5">
+        <v>651899.0499973297</v>
+      </c>
+      <c r="O4" s="4">
+        <v>82.93881043223024</v>
+      </c>
+      <c r="P4" s="5">
+        <v>7860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>50</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.454890808960443</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1831503925236359</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1850897860631577</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.85009718173002</v>
+      </c>
+      <c r="L5" s="4">
+        <v>66.21923937360026</v>
+      </c>
+      <c r="M5" s="5">
+        <v>28</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1270373.911619186</v>
+      </c>
+      <c r="O5" s="4">
+        <v>151.9767809091023</v>
+      </c>
+      <c r="P5" s="5">
+        <v>8359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4709945303882</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3295329023751145</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2819363647425585</v>
+      </c>
+      <c r="K6" s="4">
+        <v>73.80344995140926</v>
+      </c>
+      <c r="L6" s="4">
+        <v>61.4669223394058</v>
+      </c>
+      <c r="M6" s="5">
+        <v>28</v>
+      </c>
+      <c r="N6" s="5">
+        <v>768756.471157074</v>
+      </c>
+      <c r="O6" s="4">
+        <v>91.98952628420174</v>
+      </c>
+      <c r="P6" s="5">
+        <v>8357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="C7" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="D7" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3232553676988738</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1797792924676367</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1594856736306088</v>
+      </c>
+      <c r="K7" s="4">
+        <v>86.57434402332363</v>
+      </c>
+      <c r="L7" s="4">
+        <v>80.49936081815362</v>
+      </c>
+      <c r="M7" s="5">
+        <v>28</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1975750.643730164</v>
+      </c>
+      <c r="O7" s="4">
+        <v>368.335317623073</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5368497934622541</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.326863192521893</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2414801679030152</v>
+      </c>
+      <c r="K8" s="4">
+        <v>63.4037900874637</v>
+      </c>
+      <c r="L8" s="4">
+        <v>44.24736337488044</v>
+      </c>
+      <c r="M8" s="5">
+        <v>28</v>
+      </c>
+      <c r="N8" s="5">
+        <v>264703.1228542328</v>
+      </c>
+      <c r="O8" s="4">
+        <v>25.49389606609196</v>
+      </c>
+      <c r="P8" s="5">
+        <v>10383</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5340643105527748</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3898915024676342</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.540061608233391</v>
+      </c>
+      <c r="K9" s="4">
+        <v>62.86443148688071</v>
+      </c>
+      <c r="L9" s="4">
+        <v>44.47307446468471</v>
+      </c>
+      <c r="M9" s="5">
+        <v>28</v>
+      </c>
+      <c r="N9" s="5">
+        <v>361409.6887111664</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.34345315168986</v>
+      </c>
+      <c r="P9" s="5">
+        <v>10839</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>60.71428571428571</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D10" s="3">
+        <v>32.14285714285715</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>32.14285714285715</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3136855723953082</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1241047732985496</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2049805586494492</v>
+      </c>
+      <c r="K10" s="4">
+        <v>80.70456754130211</v>
+      </c>
+      <c r="L10" s="4">
+        <v>70.29082774049323</v>
+      </c>
+      <c r="M10" s="5">
+        <v>28</v>
+      </c>
+      <c r="N10" s="5">
+        <v>602329.9250602722</v>
+      </c>
+      <c r="O10" s="4">
+        <v>88.59095823801621</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>35.71428571428572</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D11" s="3">
+        <v>60.71428571428571</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F11" s="3">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.629071371708764</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3202212854906589</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2563733399644471</v>
+      </c>
+      <c r="K11" s="4">
+        <v>76.70796890184656</v>
+      </c>
+      <c r="L11" s="4">
+        <v>57.63942154042881</v>
+      </c>
+      <c r="M11" s="5">
+        <v>28</v>
+      </c>
+      <c r="N11" s="5">
+        <v>410248.3334541321</v>
+      </c>
+      <c r="O11" s="4">
+        <v>48.96733509836859</v>
+      </c>
+      <c r="P11" s="5">
+        <v>8378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D12" s="3">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F12" s="3">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.6037658756419161</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.126387660781599</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1851103248576038</v>
+      </c>
+      <c r="K12" s="4">
+        <v>72.98226433430528</v>
+      </c>
+      <c r="L12" s="4">
+        <v>49.1395014381588</v>
+      </c>
+      <c r="M12" s="5">
+        <v>28</v>
+      </c>
+      <c r="N12" s="5">
+        <v>250221.3883399963</v>
+      </c>
+      <c r="O12" s="4">
+        <v>26.83914923736955</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D13" s="3">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.526511479324859</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3374607356826758</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2223089780499927</v>
+      </c>
+      <c r="K13" s="4">
+        <v>65.30126336248814</v>
+      </c>
+      <c r="L13" s="4">
+        <v>50.20813358900565</v>
+      </c>
+      <c r="M13" s="5">
+        <v>28</v>
+      </c>
+      <c r="N13" s="5">
+        <v>733397.5925445557</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.82701757042034</v>
+      </c>
+      <c r="P13" s="5">
+        <v>9934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D14" s="3">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3220566380174346</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1552587117458698</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4509184940625529</v>
+      </c>
+      <c r="K14" s="4">
+        <v>63.14625850340131</v>
+      </c>
+      <c r="L14" s="4">
+        <v>58.97690955576854</v>
+      </c>
+      <c r="M14" s="5">
+        <v>28</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5599685.429334641</v>
+      </c>
+      <c r="O14" s="4">
+        <v>591.7452635881476</v>
+      </c>
+      <c r="P14" s="5">
+        <v>9463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.6663972160393474</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2798762488327502</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2847637076953525</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.10811467444125</v>
+      </c>
+      <c r="L15" s="4">
+        <v>68.50551294343352</v>
+      </c>
+      <c r="M15" s="5">
+        <v>28</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3632963.635206223</v>
+      </c>
+      <c r="O15" s="4">
+        <v>529.4321823384178</v>
+      </c>
+      <c r="P15" s="5">
+        <v>6862</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D16" s="3">
+        <v>67.85714285714286</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="F16" s="3">
+        <v>60.71428571428571</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5088932878851653</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.341442470119927</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4393206877488239</v>
+      </c>
+      <c r="K16" s="4">
+        <v>61.98979591836753</v>
+      </c>
+      <c r="L16" s="4">
+        <v>58.37088526685884</v>
+      </c>
+      <c r="M16" s="5">
+        <v>28</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1128071.286439896</v>
+      </c>
+      <c r="O16" s="4">
+        <v>110.4112054849658</v>
+      </c>
+      <c r="P16" s="5">
+        <v>10217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="C17" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F17" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.6458268048444934</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2870391101426957</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2917000546672983</v>
+      </c>
+      <c r="K17" s="4">
+        <v>83.25437317784258</v>
+      </c>
+      <c r="L17" s="4">
+        <v>70.61241610738205</v>
+      </c>
+      <c r="M17" s="5">
+        <v>28</v>
+      </c>
+      <c r="N17" s="5">
+        <v>739623.2533454895</v>
+      </c>
+      <c r="O17" s="4">
+        <v>110.6723407669444</v>
+      </c>
+      <c r="P17" s="5">
+        <v>6683</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3215,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3297,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3561,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3611,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3781,13 +5901,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3831,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +5967,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>14</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>8</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>7</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>22</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>12</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>26</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>16</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>17</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>5</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>8</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>19</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>19</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>18</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>18</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>14</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>14</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>13</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>13</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>5</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>19</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>17</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>13</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>13</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>5</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6735,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6777,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6808,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4821285120148218</v>
@@ -3960,10 +6867,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4821285120148218</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05198942847320609</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9174181307528279</v>
@@ -4001,10 +6924,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9174181307528279</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2238017675377932</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4889024073556685</v>
@@ -4042,9 +6981,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4889024073556685</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2021042139971598</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7010,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7029,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7071,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7102,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2686253181595362</v>
@@ -4173,10 +7161,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.09004359179581505</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2268943093913159</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1700770156809359</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.684654963757055</v>
@@ -4214,10 +7220,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.684654963757055</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.134150386455076</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3541769756810077</v>
@@ -4255,9 +7277,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3541769756810077</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2811015875780924</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7306,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7325,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7367,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7398,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2053706530907448</v>
@@ -4386,10 +7457,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0699678797874886</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2176669488555907</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1019960277154597</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8375834787043017</v>
@@ -4427,10 +7516,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8375834787043017</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3174089869811496</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3357802059997539</v>
@@ -4468,9 +7573,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3357802059997539</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1706233452783863</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7602,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7621,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7663,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7694,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.362424193968252</v>
@@ -4599,10 +7753,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.281760854345085</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2264068755234272</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2907075607551961</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8033090434968434</v>
@@ -4640,10 +7812,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8033090434968434</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4595482167144572</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4104440782404153</v>
@@ -4681,9 +7869,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4104440782404153</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2771682712756084</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7898,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7917,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7959,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +7990,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2116923442978418</v>
@@ -4812,10 +8049,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1867013339738605</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.163377036649988</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.163377036649988</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6538673290458077</v>
@@ -4853,10 +8108,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6538673290458077</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3267145949938879</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1964620833677802</v>
@@ -4894,9 +8165,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1234552516137484</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1702859964062576</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.126814460976572</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8196,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3564645006817482</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3608445920374083</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1796284445782435</v>
-      </c>
-      <c r="E3" s="4">
-        <v>71.92857142857143</v>
-      </c>
-      <c r="F3" s="4">
-        <v>58.16778523489933</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8896515554661575</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3337874662224686</v>
-      </c>
-      <c r="E4" s="4">
-        <v>51.5759637188211</v>
-      </c>
-      <c r="F4" s="4">
-        <v>24.88068605518244</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>9</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3844761345478019</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2928817930063777</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2178970066110859</v>
-      </c>
-      <c r="E5" s="4">
-        <v>65.759637188209</v>
-      </c>
-      <c r="F5" s="4">
-        <v>48.14690529455545</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4679074398178614</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3898915024676342</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4381049995164631</v>
-      </c>
-      <c r="E3" s="4">
-        <v>66.49319727891159</v>
-      </c>
-      <c r="F3" s="4">
-        <v>52.73601789709147</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6896359744594255</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.667213346639067</v>
-      </c>
-      <c r="E4" s="4">
-        <v>57.73998488284225</v>
-      </c>
-      <c r="F4" s="4">
-        <v>37.4011931394485</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>9</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4520002807960282</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5261949906243015</v>
-      </c>
-      <c r="E5" s="4">
-        <v>63.95691609977339</v>
-      </c>
-      <c r="F5" s="4">
-        <v>42.36390753169331</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>9</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>9</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/MeffordInterpreting2019.xlsx
+++ b/public/downloads/MeffordInterpreting2019.xlsx
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1667755480097162</v>
+        <v>0.1508990488622999</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
@@ -2249,13 +2249,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.108547192029835</v>
+        <v>0.1175255638655939</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2371888087044905</v>
+        <v>0.2381864055751304</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1772433323515642</v>
@@ -2431,16 +2431,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2373213160390378</v>
+        <v>0.08270380457025794</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3263166011234284</v>
+        <v>0.2726951487734254</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2545256931624998</v>
+        <v>0.2009439447499858</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3315,16 +3315,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1418530639734317</v>
+        <v>0.05567277125584269</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2525430630511768</v>
+        <v>0.2697791215946946</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1968373716792405</v>
+        <v>0.1796013131357227</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3611,16 +3611,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2632770284753286</v>
+        <v>-0.3873948865362031</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3870758785241752</v>
+        <v>0.383158011501784</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2474090632698549</v>
+        <v>0.1995066655455779</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -3727,16 +3727,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1970388822756064</v>
+        <v>-0.2779806446368411</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3935780404470614</v>
+        <v>0.3845845112958131</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1654530840932978</v>
+        <v>0.1492647316210508</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -3909,16 +3909,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1862088149317177</v>
+        <v>0.4167236915109673</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3945830925578545</v>
+        <v>0.2597476007738063</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4566194602550523</v>
+        <v>0.325257402634506</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -4205,16 +4205,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1115000999891489</v>
+        <v>-0.2362453130105919</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3990586195085172</v>
+        <v>0.3571306162509959</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.264649491935435</v>
+        <v>0.2336439256828454</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -4515,10 +4515,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.73637251960199</v>
+        <v>0.7314290471967796</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4295994536906636</v>
+        <v>0.4223461895647536</v>
       </c>
       <c r="J4" s="4">
         <v>0.7475175383073979</v>
@@ -4565,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.454890808960443</v>
+        <v>0.4507438164576293</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1831503925236359</v>
+        <v>0.1795037786089852</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1850897860631577</v>
+        <v>0.1808296400543574</v>
       </c>
       <c r="K5" s="4">
         <v>76.85009718173002</v>
@@ -4615,13 +4615,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4709945303882</v>
+        <v>0.4712799989233584</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3295329023751145</v>
+        <v>0.3259149369063721</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2819363647425585</v>
+        <v>0.2770180724295029</v>
       </c>
       <c r="K6" s="4">
         <v>73.80344995140926</v>
@@ -4665,13 +4665,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3232553676988738</v>
+        <v>0.3207951882256635</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1797792924676367</v>
+        <v>0.1757257635926418</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1594856736306088</v>
+        <v>0.1539178510480192</v>
       </c>
       <c r="K7" s="4">
         <v>86.57434402332363</v>
@@ -4815,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3136855723953082</v>
+        <v>0.3140062285322996</v>
       </c>
       <c r="I10" s="4">
         <v>0.1241047732985496</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2049805586494492</v>
+        <v>0.2059295836380484</v>
       </c>
       <c r="K10" s="4">
         <v>80.70456754130211</v>
@@ -4865,13 +4865,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.629071371708764</v>
+        <v>0.6099208530123345</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3202212854906589</v>
+        <v>0.2934304112844018</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2563733399644471</v>
+        <v>0.2278220418875065</v>
       </c>
       <c r="K11" s="4">
         <v>76.70796890184656</v>
@@ -5015,13 +5015,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3220566380174346</v>
+        <v>0.328212373211548</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1552587117458698</v>
+        <v>0.1444861751561712</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4509184940625529</v>
+        <v>0.4386070236743259</v>
       </c>
       <c r="K14" s="4">
         <v>63.14625850340131</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.6663972160393474</v>
+        <v>0.6621072005898779</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2798762488327502</v>
+        <v>0.2535650953536862</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2847637076953525</v>
+        <v>0.2502487877598137</v>
       </c>
       <c r="K15" s="4">
         <v>80.10811467444125</v>
@@ -5115,13 +5115,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.5088932878851653</v>
+        <v>0.4607377551051481</v>
       </c>
       <c r="I16" s="4">
-        <v>0.341442470119927</v>
+        <v>0.2593411841070855</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4393206877488239</v>
+        <v>0.4376144687092273</v>
       </c>
       <c r="K16" s="4">
         <v>61.98979591836753</v>
@@ -5165,13 +5165,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.6458268048444934</v>
+        <v>0.6308525179668072</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2870391101426957</v>
+        <v>0.2727288487953467</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2917000546672983</v>
+        <v>0.2684018139780181</v>
       </c>
       <c r="K17" s="4">
         <v>83.25437317784258</v>
@@ -7162,16 +7162,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.09004359179581505</v>
+        <v>0.1770827613067354</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2268943093913159</v>
+        <v>0.2130525866567268</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1700770156809359</v>
+        <v>0.1576428486079473</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -7458,16 +7458,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0699678797874886</v>
+        <v>-0.03743628215065087</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2176669488555907</v>
+        <v>0.2060553698477122</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1019960277154597</v>
+        <v>0.09348726191460817</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.281760854345085</v>
+        <v>0.2129047619623066</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2264068755234272</v>
+        <v>0.2272061874218707</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2907075607551961</v>
+        <v>0.2834716298177113</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -8050,16 +8050,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1867013339738605</v>
+        <v>0.136710469552014</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.163377036649988</v>
+        <v>0.1547221773124988</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.163377036649988</v>
+        <v>0.1547221773124988</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -8166,16 +8166,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1234552516137484</v>
+        <v>0.1437478616137469</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1702859964062576</v>
+        <v>0.1722486150868134</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.126814460976572</v>
+        <v>0.1264858307421974</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
